--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0087.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0087.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Chưa ghi nhận</t>
+          <t>Chưa ghi lại</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Chưa có Điểm Câu Cá nào có thể truy vết</t>
+          <t>Chưa phát hiện Điểm Câu Cá nào có thể theo dõi</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Ability Required</t>
+          <t>Yêu Cầu Kỹ Năng</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Fish King</t>
+          <t>Vua Cá</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Vật Liệu</t>
+          <t>Vật liệu</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>Thường</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Mutant</t>
+          <t>Đột biến</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Không thể đặt vào Hàng Hóa Tạm Thời trong trạng thái này</t>
+          <t>Không thể đặt vào Hàng Hóa Tạm thời trong trạng thái này</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Fishing Time</t>
+          <t>Giờ Câu Cá</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Finished</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Show Recorded Entries</t>
+          <t>Hiển thị Nhật Ký Đã Ghi</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Not Recorded</t>
+          <t>Chưa ghi lại</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Recorded</t>
+          <t>Đã ghi lại</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Chưa mở khóa Kỹ Năng tương ứng</t>
+          <t>Khả năng tương ứng chưa được mở khóa.</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Bong Bóng Kỳ Diệu đã đầy</t>
+          <t>Bong Bóng Kỳ Diệu đã đầy rồi</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Lưới Kéo đã đầy</t>
+          <t>Lưới đã đầy</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Đây không phải là điểm giao hàng</t>
+          <t>Đây không phải địa điểm giao hàng.</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Giao những mẻ bắt được tại bến tàu để hoàn thành Yêu cầu</t>
+          <t>Giao hàng tại bến tàu để hoàn thành Yêu Cầu</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Siren's Boneyard</t>
+          <t>Nghĩa Địa Siran</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Darkblight Ruins</t>
+          <t>Tàn Tích Hắc Ám</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Mistbound Lair</t>
+          <t>Hang Sương Mù Trói Buộc</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Weeping Walkway</t>
+          <t>Hành Lang Than Khóc</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Starfall Expanse</t>
+          <t>Vùng Đất Starfall</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Burial Bay</t>
+          <t>Vịnh An Táng</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Doomstrand</t>
+          <t>Sợi Dây Định Mệnh</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Whirlpool</t>
+          <t>Vực Xoáy</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Riptide</t>
+          <t>Dòng Chảy Xoáy</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Tempest</t>
+          <t>Bão Tố</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Infinite Torrents</t>
+          <t>Hồng Thủy Vô Tận</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Đạt tổng cộng 1.600 điểm trong Forbidden Waters</t>
+          <t>Đạt tổng 1.600 điểm tại Vùng Cấm Thủy</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Đạt tổng cộng 3.200 điểm trong Forbidden Waters</t>
+          <t>Đạt tổng 3.200 điểm tại Forbidden Waters</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Đạt tổng cộng 4.800 điểm trong Forbidden Waters</t>
+          <t>Đạt tổng 4.800 điểm tại Forbidden Waters</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Đạt tổng cộng 5.000 điểm trong Respawning Waters: Chasm</t>
+          <t>Đạt tổng 5.000 điểm tại Respawning Waters: Chasm</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Đạt tổng cộng 12.000 điểm trong Respawning Waters: Chasm</t>
+          <t>Đạt tổng 12.000 điểm tại Vực Nước Tái Sinh: Hẻm Núi</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Đạt tổng cộng 15.000 điểm trong Respawning Waters: Chasm</t>
+          <t>Đạt tổng 15.000 điểm tại Vực Nước Tái Sinh: Hẻm Núi</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Đạt tổng cộng 3.500 điểm trong Respawning Waters: Torrents</t>
+          <t>Đạt tổng 3.500 điểm tại Respawning Waters: Torrents</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Đạt tổng cộng 4.000 điểm trong Respawning Waters: Torrents</t>
+          <t>Đạt tổng 4.000 điểm tại Respawning Waters: Torrents</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Đạt tổng cộng 4.500 điểm trong Respawning Waters: Torrents</t>
+          <t>Đạt tổng 4.500 điểm tại Respawning Waters: Torrents</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Forbidden Waters</t>
+          <t>Vùng Nước Cấm</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Respawning Waters: Chasm</t>
+          <t>Suối Tái Sinh: Vực Sâu</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Respawning Waters: Torrents</t>
+          <t>Dòng Nước Tái Sinh: Thủy Triều</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Respawning Waters</t>
+          <t>Suối Tái Sinh</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Fishing Adventure</t>
+          <t>Cuộc Phiêu Lưu Câu Cá</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>Đi thôi</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Hoàn thành Chương II Prologue để trải nghiệm trước</t>
+          <t>Hoàn thành Lời Mở Đầu Chương II để trải nghiệm trước</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Hoàn thành Chương II Prologue "Through the Sea Thou Break"</t>
+          <t>Hoàn thành Lời Mở Đầu Chương II "Vượt Biển Tới Chân Trời"</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Priority Request</t>
+          <t>Yêu Cầu Ưu Tiên</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Premium Request</t>
+          <t>Yêu Cầu Cao Cấp</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Quick Sale Request</t>
+          <t>Yêu cầu bán nhanh</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Common Request</t>
+          <t>Yêu cầu thông thường</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Personal Request</t>
+          <t>Yêu Cầu Cá Nhân</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Key Fishing Ability</t>
+          <t>Kỹ Năng Câu Cá Chính</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Primary Fishing Ability</t>
+          <t>Kỹ Năng Câu Cá Cơ Bản</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Secondary Fishing Ability</t>
+          <t>Kỹ Năng Câu Cá Phụ</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Original Species</t>
+          <t>Loài ban đầu</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Mutation</t>
+          <t>Đột biến</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Vật liệu không đủ</t>
+          <t>Nguyên liệu không đủ.</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Required Nodes Locked</t>
+          <t>Các Nút yêu cầu đang bị khóa</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Làm mới sau 1 giờ</t>
+          <t>Làm mới sau 1 giờ nữa</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Vùng Đất Than Thở</t>
+          <t>Vùng Đất Than Khóc</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Vùng Đất Than Thở</t>
+          <t>Vùng Đất Than Khóc</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Ảo tưởng Ngàn Cánh Cổng</t>
+          <t>Những Ảo Ảnh Ngàn Cánh Cổng</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Clear Goal</t>
+          <t>Hoàn thành Mục Tiêu</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Điểm đạt</t>
+          <t>Đạt Mức Điểm</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Mục tiêu thử thách</t>
+          <t>Mục Tiêu Thử Thách</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Create Frequency</t>
+          <t>Tạo Tần Số Mới</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Record</t>
+          <t>Ghi Chép</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Kỷ lục trước đó</t>
+          <t>Bản ghi trước</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Date Achieved</t>
+          <t>Ngày Đạt Được</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Kỷ lục đã được cập nhật</t>
+          <t>Bản ghi đã được cập nhật</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Tất cả đội phải mang theo một Token</t>
+          <t>Mọi đội phải mang theo một Token.</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Thông tin giai đoạn</t>
+          <t>Thông Tin Giai Đoạn</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Chi tiết Resonator</t>
+          <t>Thông Tin Resonator</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Bắt đầu thử thách</t>
+          <t>Bắt đầu Thử thách</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Thử thách lại</t>
+          <t>Thử Thách Lại</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Countdown</t>
+          <t>Đếm Ngược</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Hoàn thành "Tình yêu thời câu cá"</t>
+          <t>Hoàn thành "Love in the Time of Fishing"</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Complete "Where Tất cả Fish Converge"</t>
+          <t>Hoàn thành "Nơi Vạn Cá Hội Tụ".</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Hoàn thành "Ông lão và cá voi"</t>
+          <t>Hoàn thành "Ông Già và Cá Voi"</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Complete "Old Captain's Log I"</t>
+          <t>Hoàn thành "Nhật Ký Thuyền Trưởng Cũ I"</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Complete "Old Captain's Log II"</t>
+          <t>Hoàn thành "Nhật Ký Thuyền Trưởng Cũ II"</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Đạt 100% tiến độ sửa chữa tàu lớn</t>
+          <t>Hoàn thành 100% tiến độ sửa chữa tàu lớn</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Nhận tổng cộng 1.000 Riccioli Fishery Coin</t>
+          <t>Thu thập tổng cộng 1.000 Xu Riccioli Fishery</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Nhận tổng cộng 10.000 Riccioli Fishery Coin</t>
+          <t>Thu thập tổng cộng 10.000 Riccioli Fishery Coin</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Nhận tổng cộng 100.000 Riccioli Fishery Coin</t>
+          <t>Thu thập tổng cộng 100.000 Đồng Riccioli Fishery</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Nhận tổng cộng 200.000 Riccioli Fishery Coin</t>
+          <t>Thu thập tổng cộng 200.000 Xu Công Ty Riccioli Fishery</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Bắt được 1 loại Fish King</t>
+          <t>Bắt 1 loại Cá Vua</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Bắt được 3 loại Fish Kings</t>
+          <t>Bắt 3 loại Cá Vua</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Bắt được 5 loại Fish Kings</t>
+          <t>Bắt 5 loại Cá Vua</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Bắt được 1 loại Mutant</t>
+          <t>Bắt 1 loại Mutant</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Bắt được 5 loại Mutants</t>
+          <t>Bắt 5 loại Cá Đột Biến</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Bắt được 10 loại Mutants</t>
+          <t>Bắt 10 loại Mutant</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Finish 4 Priority Requests</t>
+          <t>Hoàn thành 4 Yêu Cầu Ưu Tiên</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Finish 8 Priority Requests</t>
+          <t>Hoàn thành 8 Yêu Cầu Ưu Tiên</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8414,7 +8414,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Finish 12 Priority Requests</t>
+          <t>Hoàn thành 12 Yêu Cầu Ưu Tiên</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8484,7 +8484,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Hoàn thành tất cả Priority Requests</t>
+          <t>Hoàn thành tất cả Yêu Cầu Ưu Tiên</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Finish 1 Common Request</t>
+          <t>Hoàn thành 1 Yêu cầu Thường</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Finish 5 Common Requests</t>
+          <t>Hoàn thành 5 Yêu Cầu Thường</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Finish 10 Common Requests</t>
+          <t>Hoàn thành 10 Yêu cầu Thường</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Complete 1 Premium Request</t>
+          <t>Hoàn thành 1 Yêu Cầu Cao Cấp</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Complete 2 Premium Requests</t>
+          <t>Hoàn thành 2 Yêu Cầu Cao Cấp</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Complete 5 Premium Requests</t>
+          <t>Hoàn thành 5 Nhiệm Vụ Cao Cấp.</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Mở Khóa Thân Tàu Nâng Cao</t>
+          <t>Mở khóa Thân Tàu Cao Cấp</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Mở Khóa Thân Tàu Vực Sâu</t>
+          <t>Mở khóa Thân Tàu Vực Sâu</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Mở Khóa Thân Tàu Đại Dương</t>
+          <t>Mở khóa Thân Tàu Đại Dương</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Mở Khóa 2 Kỹ Năng Câu Cá Phụ</t>
+          <t>Mở khóa 2 Kỹ Năng Câu Cá Phụ</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Mở Khóa 4 Kỹ Năng Câu Cá Phụ</t>
+          <t>Mở khóa 4 Kỹ Năng Câu Cá Phụ</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Mở Khóa 6 Kỹ Năng Câu Cá Phụ</t>
+          <t>Mở khóa 6 Kỹ năng Câu Cá Phụ</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Mở khóa tất cả Fishing Abilities</t>
+          <t>Mở khóa tất cả Kỹ năng Câu cá.</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Rover học được 1 Fishing Ability</t>
+          <t>Vận Mệnh Giả học được 1 Kỹ Năng Câu Cá</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Rover học được tất cả Fishing Abilities</t>
+          <t>Vận Mệnh Giả học được toàn bộ Kỹ Năng Câu Cá</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9604,7 +9604,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Phoebe học được 1 Fishing Ability</t>
+          <t>Phoebe học được 1 Kỹ Năng Câu Cá.</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Phoebe học được tất cả Fishing Abilities</t>
+          <t>Phoebe học được tất cả Kỹ Năng Câu Cá.</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Mở Khóa Phòng Máy Bổ Sung</t>
+          <t>Mở khóa Phòng Máy Phụ</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Mở khóa 5 mục trong Index</t>
+          <t>Mở khóa 5 mục trong Chỉ Mục</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Mở khóa 50 mục trong Mục Lục</t>
+          <t>Mở khóa 50 mục trong Chỉ Mục</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Mở khóa 5 Cúp Vàng trong Mục Lục</t>
+          <t>Mở khóa 5 Cúp Vàng trong Chỉ Mục</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10164,7 +10164,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Mở khóa 10 Cúp Vàng trong Mục Lục</t>
+          <t>Mở khóa 10 Cúp Vàng trong Chỉ Số</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Mở khóa 5 Cúp Bạc trong Mục Lục</t>
+          <t>Mở khóa 5 Cúp Bạc trong Chỉ Mục</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Mở khóa 10 Cúp Bạc trong Mục Lục</t>
+          <t>Mở khóa 10 Cúp Bạc trong Chỉ Số</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Dispel 1 Ghost Medusa</t>
+          <t>Tiêu diệt 1 Ghost Medusa</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Thu hoạch Bong Bóng Kỳ Diệu 20 lần</t>
+          <t>Thu thập Bong bóng Kỳ Diệu 20 lần</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Sử dụng "Sweet Puff" 1 lần</t>
+          <t>Dùng "Sweet Puff" 1 lần</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Mở Khóa Niềm Tin Thủy Thủ</t>
+          <t>Mở khóa Niềm Tin Của Thủy Thủ.</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Mở khóa Đức Tin Đoàn Kết</t>
+          <t>Mở khóa Niềm Tin Đoàn Kết</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Mở Khóa Dũng Khí Phá Triều</t>
+          <t>Mở khóa Dũng Khí của Tidebreaker</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -10864,7 +10864,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Mở Khóa Sự Thôi Thúc Báo Thù</t>
+          <t>Mở khóa Thôi Thúc Báo Thù</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Hoàn thành Bán Nhanh 1 lần</t>
+          <t>Thực hiện Bán nhanh 1 lần</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11004,7 +11004,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Hoàn thành Bán Nhanh 10 lần</t>
+          <t>Thực hiện Bán nhanh 10 lần</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Penitent's End</t>
+          <t>Kết Cục Của Kẻ Ăn Năn</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Atrium of Reflections</t>
+          <t>Đại Sảnh Phản Chiếu</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11354,7 +11354,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Silver Moon Grove</t>
+          <t>Lâm Nguyệt Bạc</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11424,7 +11424,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Shores of Last Breath</t>
+          <t>Bờ Biển Hơi Thở Cuối Cùng</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11494,7 +11494,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Như Gió</t>
+          <t>Như gió vậy</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11564,7 +11564,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Vượt Cự Ly Nhanh</t>
+          <t>Đột Kích Vượt Tuyến</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11634,7 +11634,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Gotta Go Fast</t>
+          <t>Phải nhanh lên thôi!</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>The Outsider</t>
+          <t>Kẻ Ngoại Lai</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -11914,7 +11914,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Đạt hạng nhất trong cuộc đua</t>
+          <t>Đã giành vị trí đầu tiên trong cuộc đua</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -11984,7 +11984,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Người chơi hoàn thành cuộc đua trong giai đoạn nước rút cuối cùng</t>
+          <t>Những người hoàn thành cuộc đua trong thời gian đếm ngược nước rút cuối cùng</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Người chơi đạt 75%~100% tiến trình đường đua</t>
+          <t>Những {PlayerName} hoàn thành 75%~100% đường đua</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Người chơi không hoàn thành cuộc đua</t>
+          <t>Những {PlayerName} không hoàn thành cuộc đua</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Không. 1</t>
+          <t>Số 1</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12264,7 +12264,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Không. 2</t>
+          <t>Số 2</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -12334,7 +12334,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Không. 3</t>
+          <t>Số 3</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Điểm cao nhất của sân khấu</t>
+          <t>Đỉnh cao của sân khấu</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Highest Ranking of the Stage</t>
+          <t>Xếp Hạng Cao Nhất Của Giai Đoạn</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -12544,7 +12544,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Apex Ragunna</t>
+          <t>Ragunna Đỉnh Cao</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -12614,7 +12614,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Past Lessons</t>
+          <t>Quá khứ - Những Bài Học</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -12684,7 +12684,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Sailer's Conviction</t>
+          <t>Niềm Tin Của Thủy Thủ</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Tidebreaker's Valor</t>
+          <t>Dũng Khí của Tidebreaker</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -12894,7 +12894,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Vengeful Compulsion</t>
+          <t>Ám Ảnh Báo Thù</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -13104,7 +13104,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Không Record</t>
+          <t>Không có bản ghi</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Hiệu ứng Token</t>
+          <t>Hiệu ứng Mã Đổi</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13314,7 +13314,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Nửa đầu</t>
+          <t>Hiệp Một</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -13384,7 +13384,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Nửa sau</t>
+          <t>Hiệp Hai</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13454,7 +13454,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Respawning Waters Refresh Time</t>
+          <t>Thời gian Làm mới Suối Tái Sinh</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Phần thưởng Vùng Nước Cấm</t>
+          <t>Phần Thưởng Vùng Nước Cấm</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Phần thưởng Vùng Nước Hồi Sinh</t>
+          <t>Phần thưởng Suối Tái Sinh</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -13734,7 +13734,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Rời khỏi</t>
+          <t>Rời đi</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -13804,7 +13804,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Thử thách lại</t>
+          <t>Thử Thách Lại</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Ranking Points</t>
+          <t>Điểm xếp hạng</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -13944,7 +13944,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Course Completion Points</t>
+          <t>Điểm Hoàn Thành Khóa Học</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14014,7 +14014,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Điểm Hiện Tại</t>
+          <t>Điểm hiện tại</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14154,7 +14154,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Vùng Nước trước chưa hoàn thành</t>
+          <t>Vùng Preceding Waters chưa được thông qua</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14224,7 +14224,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Vùng Đất Than Thở</t>
+          <t>Vùng Đất Than Khóc</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -14294,7 +14294,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Vùng Đất Than Thở</t>
+          <t>Vùng Đất Than Khóc</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14434,7 +14434,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Không có yêu cầu nào được theo dõi</t>
+          <t>Không có yêu cầu nào đang được theo dõi</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -14504,7 +14504,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Sắp xếp theo số thứ tự</t>
+          <t>Sắp xếp theo Số Thứ Tự</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Không xác định</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -14644,7 +14644,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Nam</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Troupe of Fools</t>
+          <t>Đoàn Hội Ngớ Ngẩn</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -14854,7 +14854,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Flamebound Compass</t>
+          <t>La Bàn Gắn Bó Với Lửa</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -15204,7 +15204,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Không xác định</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Nữ</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15414,7 +15414,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Giáo Đoàn Vực Sâu</t>
+          <t>Lệnh của Vực Sâu</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -15484,7 +15484,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Graceful Luminescence</t>
+          <t>Ánh Sáng Dịu Dàng</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>The Initial Treasure</t>
+          <t>Kho Báu Đầu Tiên</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -15904,7 +15904,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Tất cả the World's His Stage</t>
+          <t>Cả Thế Giới Là Sân Khấu Của Người</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Testament to a Captain</t>
+          <t>Di Chúc Của Đội Trưởng</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -16044,7 +16044,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Frozen In Time</t>
+          <t>Đóng Băng Theo Thời Gian</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -16114,7 +16114,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>"Envoy"</t>
+          <t>"Sứ Giả"</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16184,7 +16184,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>A Vision Far Away</t>
+          <t>Một Tầm Nhìn Xa Xôi</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -16254,7 +16254,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>An Improvised Afternoon at the Tavern</t>
+          <t>Một Buổi Chiều Tự Sáng Tạo Tại Quán Rượu</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -16324,7 +16324,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Dusk, When Fools Sing</t>
+          <t>Chạng Vạng, Khi Kẻ Ngốc Cất Tiếng Hát</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -16394,7 +16394,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Suy Tư Bên Lửa Trại</t>
+          <t>Những Phản Chiếu Bên Lửa Trại</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -16464,7 +16464,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Vượt Qua Bão Biển</t>
+          <t>Xuyên qua Bão Biển</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -16534,7 +16534,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Khi Lễ Hội Carnevale Kết Thúc</t>
+          <t>Khi Lễ Hội Carnevale kết thúc</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -16604,7 +16604,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Một Ngày Trong Đời Tu Sĩ</t>
+          <t>Một Ngày Của Kẻ Tu Hành</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Nhà</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Countless Nights</t>
+          <t>Đêm Vô Tận</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -16814,7 +16814,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Nhưng Morning Came</t>
+          <t>Nhưng Bình Minh Vẫn Đến</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -16884,7 +16884,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Within Distant Brilliance</t>
+          <t>Trong Ánh Sáng Viễn Xứ</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -25494,7 +25494,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Ability Activated</t>
+          <t>Kích Hoạt Kỹ Năng</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
@@ -25564,7 +25564,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Quick Launch</t>
+          <t>Khởi động nhanh</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
@@ -25634,7 +25634,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Xem Yêu cầu</t>
+          <t>Xem Yêu Cầu</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
@@ -25704,7 +25704,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Vùng Đất Than Thở</t>
+          <t>Vùng Đất Than Khóc</t>
         </is>
       </c>
       <c r="N361" t="inlineStr">
@@ -25774,7 +25774,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Overworld Exploration</t>
+          <t>Khám Phá Thế Giới Mở</t>
         </is>
       </c>
       <c r="N362" t="inlineStr">
@@ -25844,7 +25844,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Resonators</t>
+          <t>Resonator</t>
         </is>
       </c>
       <c r="N363" t="inlineStr">
@@ -25914,7 +25914,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Preset Teams</t>
+          <t>Đội Hình Cài Đặt</t>
         </is>
       </c>
       <c r="N364" t="inlineStr">
@@ -25984,7 +25984,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Yêu Cầu</t>
+          <t>Nhận</t>
         </is>
       </c>
       <c r="N365" t="inlineStr">
@@ -26194,7 +26194,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Số lần sử dụng mã thông báo:</t>
+          <t>Số lần sử dụng Mã Đổi:</t>
         </is>
       </c>
       <c r="N368" t="inlineStr">
@@ -26264,7 +26264,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Trang Bị</t>
+          <t>Trang bị</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
@@ -26404,7 +26404,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Apply</t>
+          <t>Áp dụng</t>
         </is>
       </c>
       <c r="N371" t="inlineStr">
@@ -26544,7 +26544,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Insufficient "Sweet Puffs"</t>
+          <t>"Bánh Ngọt Xốp" không đủ</t>
         </is>
       </c>
       <c r="N373" t="inlineStr">
@@ -26614,7 +26614,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Sandworm đã kích hoạt</t>
+          <t>Giun Cát đã phóng</t>
         </is>
       </c>
       <c r="N374" t="inlineStr">
@@ -26684,7 +26684,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>"Sweet Puff" đã kích hoạt</t>
+          <t>"\"Bánh Ngọt Puff\" đã phóng!"</t>
         </is>
       </c>
       <c r="N375" t="inlineStr">
@@ -26754,7 +26754,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Sinh Vật Biển Bị Thu Hút Bởi Sandworm</t>
+          <t>Sinh Vật Biển Bị Mồi Bẫy Bởi Giun Cát</t>
         </is>
       </c>
       <c r="N376" t="inlineStr">
@@ -26894,7 +26894,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Đến bến tàu để nhận yêu cầu mới</t>
+          <t>Đến bến tàu để nhận nhiệm vụ mới</t>
         </is>
       </c>
       <c r="N378" t="inlineStr">
@@ -26964,7 +26964,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Phần Thưởng Hiện Tại</t>
+          <t>Phần thưởng hiện tại</t>
         </is>
       </c>
       <c r="N379" t="inlineStr">
@@ -27034,7 +27034,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Điểm Ảo Ảnh hiện tại</t>
+          <t>Điểm Ảo Ảnh Hiện Tại</t>
         </is>
       </c>
       <c r="N380" t="inlineStr">
@@ -27104,7 +27104,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Vùng Đất Than Thở</t>
+          <t>Vùng Đất Than Khóc</t>
         </is>
       </c>
       <c r="N381" t="inlineStr">
@@ -27244,7 +27244,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Tiến độ</t>
         </is>
       </c>
       <c r="N383" t="inlineStr">
@@ -27314,7 +27314,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Illusive Points Obtained</t>
+          <t>Điểm Ảo Ảnh Nhận Được</t>
         </is>
       </c>
       <c r="N384" t="inlineStr">
@@ -27384,7 +27384,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Metaphor</t>
+          <t>Ẩn Dụ</t>
         </is>
       </c>
       <c r="N385" t="inlineStr">
@@ -27454,7 +27454,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Metaphor</t>
+          <t>Ẩn Dụ</t>
         </is>
       </c>
       <c r="N386" t="inlineStr">
@@ -27524,7 +27524,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Kỷ Lục Thời Gian Vượt Giai Đoạn</t>
+          <t>Kỷ lục thời gian giai đoạn</t>
         </is>
       </c>
       <c r="N387" t="inlineStr">
@@ -27594,7 +27594,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Virtual Trailblazer</t>
+          <t>Người Tiên Phong Ảo</t>
         </is>
       </c>
       <c r="N388" t="inlineStr">
@@ -27664,7 +27664,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Adversity Expeditioner</t>
+          <t>Nhà Thám Hiểm Nghịch Cảnh</t>
         </is>
       </c>
       <c r="N389" t="inlineStr">
@@ -27734,7 +27734,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Darkness Repeller</t>
+          <t>Kẻ Đẩy Lùi Bóng Tối</t>
         </is>
       </c>
       <c r="N390" t="inlineStr">
@@ -27804,7 +27804,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Chúa Tể Tháp</t>
+          <t>Chúa Tể Tháp Canh</t>
         </is>
       </c>
       <c r="N391" t="inlineStr">
@@ -27874,7 +27874,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Người Giám Sát Thủy Triều</t>
+          <t>Giám Sát Viên Của Thủy Triều</t>
         </is>
       </c>
       <c r="N392" t="inlineStr">
@@ -27944,7 +27944,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Người Gìn Giữ Biển Đêm</t>
+          <t>Người Gác Đêm Đại Dương</t>
         </is>
       </c>
       <c r="N393" t="inlineStr">
@@ -28224,7 +28224,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Howling Chainsaw</t>
+          <t>Cưa Xích Gào Thét</t>
         </is>
       </c>
       <c r="N397" t="inlineStr">
@@ -28294,7 +28294,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Raspy Radio</t>
+          <t>Radio Khàn Giọng</t>
         </is>
       </c>
       <c r="N398" t="inlineStr">
@@ -28364,7 +28364,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Lost Dance Shoes</t>
+          <t>Đôi Giày Khiêu Vũ Bị Lãng Quên</t>
         </is>
       </c>
       <c r="N399" t="inlineStr">
@@ -28434,7 +28434,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Static Noise</t>
+          <t>Tạp Âm Tĩnh</t>
         </is>
       </c>
       <c r="N400" t="inlineStr">
@@ -28504,7 +28504,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Door-smashing Axe</t>
+          <t>Rìu Phá Cửa</t>
         </is>
       </c>
       <c r="N401" t="inlineStr">
@@ -28574,7 +28574,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Winking Doll</t>
+          <t>Búp Bê Nháy Mắt</t>
         </is>
       </c>
       <c r="N402" t="inlineStr">
@@ -28644,7 +28644,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Floating Balloon</t>
+          <t>Bong Bóng Bay</t>
         </is>
       </c>
       <c r="N403" t="inlineStr">
@@ -28714,7 +28714,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Cracked Glasses</t>
+          <t>Kính Vỡ</t>
         </is>
       </c>
       <c r="N404" t="inlineStr">
@@ -28784,7 +28784,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Ominous Collection</t>
+          <t>Bộ Sưu Tập U Minh</t>
         </is>
       </c>
       <c r="N405" t="inlineStr">
@@ -28854,7 +28854,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Options:</t>
+          <t>Quyền chọn:</t>
         </is>
       </c>
       <c r="N406" t="inlineStr">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Thử Thách Giải Trí</t>
+          <t>Thử Thách Nhàn Hạ</t>
         </is>
       </c>
       <c r="N407" t="inlineStr">
@@ -28994,7 +28994,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Permanent Event</t>
+          <t>Sự kiện Vĩnh viễn</t>
         </is>
       </c>
       <c r="N408" t="inlineStr">
@@ -29064,7 +29064,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Combat Event</t>
+          <t>Sự Kiện Chiến Đấu</t>
         </is>
       </c>
       <c r="N409" t="inlineStr">
@@ -29274,7 +29274,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Permanent Event</t>
+          <t>Sự kiện Vĩnh viễn</t>
         </is>
       </c>
       <c r="N412" t="inlineStr">
@@ -29344,7 +29344,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Combat Event</t>
+          <t>Sự Kiện Chiến Đấu</t>
         </is>
       </c>
       <c r="N413" t="inlineStr">
@@ -29554,7 +29554,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Any Dock</t>
+          <t>Bến Tàu Nào Cũng Được</t>
         </is>
       </c>
       <c r="N416" t="inlineStr">
@@ -29624,7 +29624,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Solo Ranking</t>
+          <t>Bảng Xếp Hạng Solo</t>
         </is>
       </c>
       <c r="N417" t="inlineStr">
@@ -29694,7 +29694,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Co-op Ranking</t>
+          <t>Bảng Xếp hạng Đồng Đội</t>
         </is>
       </c>
       <c r="N418" t="inlineStr">
@@ -29764,7 +29764,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Anonymous</t>
+          <t>Ẩn danh</t>
         </is>
       </c>
       <c r="N419" t="inlineStr">
@@ -29974,7 +29974,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Destroy</t>
+          <t>Hủy Diệt</t>
         </is>
       </c>
       <c r="N422" t="inlineStr">
@@ -30114,7 +30114,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Proceed</t>
+          <t>Tiến lên</t>
         </is>
       </c>
       <c r="N424" t="inlineStr">
@@ -30184,7 +30184,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Avatar</t>
+          <t>Hóa Thân</t>
         </is>
       </c>
       <c r="N425" t="inlineStr">
@@ -30254,7 +30254,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Sigil</t>
+          <t>Ấn Tín</t>
         </is>
       </c>
       <c r="N426" t="inlineStr">
@@ -30324,7 +30324,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Danh Hiệu</t>
+          <t>Danh hiệu</t>
         </is>
       </c>
       <c r="N427" t="inlineStr">
@@ -30394,7 +30394,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Thường Mode</t>
+          <t>Chế Độ Thường</t>
         </is>
       </c>
       <c r="N428" t="inlineStr">
@@ -30464,7 +30464,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Full-Speed Mode</t>
+          <t>Chế Độ Tốc Độ Tối Đa</t>
         </is>
       </c>
       <c r="N429" t="inlineStr">
@@ -30534,7 +30534,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Pause</t>
+          <t>Tạm dừng</t>
         </is>
       </c>
       <c r="N430" t="inlineStr">
@@ -30744,7 +30744,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Tải xuống hoàn tất</t>
+          <t>Đã tải xong</t>
         </is>
       </c>
       <c r="N433" t="inlineStr">
@@ -30884,7 +30884,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Vui lòng xác nhận lựa chọn của bạn</t>
+          <t>Xác nhận lựa chọn của bạn</t>
         </is>
       </c>
       <c r="N435" t="inlineStr">
@@ -30954,7 +30954,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Vật liệu không đủ</t>
+          <t>Nguyên liệu không đủ</t>
         </is>
       </c>
       <c r="N436" t="inlineStr">
@@ -31024,7 +31024,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Chỉ có thể chọn Echo 5 sao chưa nâng cấp</t>
+          <t>Chỉ có thể chọn Cộng Hưởng 5 sao chưa nâng cấp</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
@@ -31094,7 +31094,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Chỉnh sửa dữ liệu</t>
+          <t>Điều Chỉnh Dữ Liệu</t>
         </is>
       </c>
       <c r="N438" t="inlineStr">
@@ -31164,7 +31164,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Mainstats Available</t>
+          <t>Chỉ Số Chính Có Sẵn</t>
         </is>
       </c>
       <c r="N439" t="inlineStr">
@@ -31234,7 +31234,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Hoàn thành giai đoạn yêu cầu để mở khóa</t>
+          <t>Hoàn thành giai đoạn yêu cầu để mở khóa.</t>
         </is>
       </c>
       <c r="N440" t="inlineStr">
@@ -31304,7 +31304,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Shield Absorption:</t>
+          <t>Hấp thụ Khiên:</t>
         </is>
       </c>
       <c r="N441" t="inlineStr">
@@ -31374,7 +31374,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Dodge Count:</t>
+          <t>Số lần né tránh:</t>
         </is>
       </c>
       <c r="N442" t="inlineStr">
@@ -31444,7 +31444,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Counterattack Count:</t>
+          <t>Số lần phản công:</t>
         </is>
       </c>
       <c r="N443" t="inlineStr">
@@ -31514,7 +31514,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Knocked Out Count:</t>
+          <t>Số Lần Hạ Gục:</t>
         </is>
       </c>
       <c r="N444" t="inlineStr">
@@ -31584,7 +31584,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Healing Contribution:</t>
+          <t>Đóng góp hồi phục:</t>
         </is>
       </c>
       <c r="N445" t="inlineStr">
@@ -31654,7 +31654,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Impregnable Fortress</t>
+          <t>Pháo Đài Bất Khả Xâm Phạm</t>
         </is>
       </c>
       <c r="N446" t="inlineStr">
@@ -31724,7 +31724,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Ethereal Form</t>
+          <t>Hình Thái Siêu Nhiên</t>
         </is>
       </c>
       <c r="N447" t="inlineStr">
@@ -31794,7 +31794,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Unbreakable Stance</t>
+          <t>Thế Trụ Bất Diệt</t>
         </is>
       </c>
       <c r="N448" t="inlineStr">
@@ -31864,7 +31864,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Bậc Thầy Rune</t>
+          <t>Chủ Ấn Pháp</t>
         </is>
       </c>
       <c r="N449" t="inlineStr">
@@ -31934,7 +31934,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Death Conqueror</t>
+          <t>Kẻ Chinh Phục Tử Thần</t>
         </is>
       </c>
       <c r="N450" t="inlineStr">
@@ -32004,7 +32004,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Nightmare Hunter</t>
+          <t>Thợ Săn Ác Mộng</t>
         </is>
       </c>
       <c r="N451" t="inlineStr">
@@ -32074,7 +32074,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Field Medic</t>
+          <t>Hộ Sĩ Chiến Trường</t>
         </is>
       </c>
       <c r="N452" t="inlineStr">
@@ -32144,7 +32144,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Bậc Thầy Bẫy</t>
+          <t>Chủ Bẫy Cơ Khí</t>
         </is>
       </c>
       <c r="N453" t="inlineStr">
@@ -32214,7 +32214,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Blazing Fury</t>
+          <t>Cơn Thịnh Nộ Rực Lửa</t>
         </is>
       </c>
       <c r="N454" t="inlineStr">
@@ -32284,7 +32284,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Inferno Rider: Ultra</t>
+          <t>Inferno Rider: Siêu Cấp</t>
         </is>
       </c>
       <c r="N455" t="inlineStr">
@@ -32354,7 +32354,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Spoiled Blaze</t>
+          <t>Lửa Tham Lam</t>
         </is>
       </c>
       <c r="N456" t="inlineStr">
@@ -32424,7 +32424,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Meteor Fire I</t>
+          <t>Hỏa Mưa Cấp I</t>
         </is>
       </c>
       <c r="N457" t="inlineStr">
@@ -32494,7 +32494,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Meteor Fire II</t>
+          <t>Hỏa Mưa Cấp II</t>
         </is>
       </c>
       <c r="N458" t="inlineStr">
@@ -32564,7 +32564,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Meteor Fire III</t>
+          <t>Hỏa Mưa Cấp III</t>
         </is>
       </c>
       <c r="N459" t="inlineStr">
@@ -32634,7 +32634,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Thorny Blade I</t>
+          <t>Lưỡi Kiếm Gai I</t>
         </is>
       </c>
       <c r="N460" t="inlineStr">
@@ -32704,7 +32704,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Thorny Blade II</t>
+          <t>Lưỡi Kiếm Gai II</t>
         </is>
       </c>
       <c r="N461" t="inlineStr">
@@ -32774,7 +32774,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Thorny Blade III</t>
+          <t>Lưỡi Kiếm Gai III</t>
         </is>
       </c>
       <c r="N462" t="inlineStr">
@@ -32844,7 +32844,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Frenzy I</t>
+          <t>Cuồng Loạn Cấp I</t>
         </is>
       </c>
       <c r="N463" t="inlineStr">
@@ -32914,7 +32914,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Frenzy II</t>
+          <t>Cuồng Loạn Cấp II</t>
         </is>
       </c>
       <c r="N464" t="inlineStr">
@@ -32984,7 +32984,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Parting Gift I</t>
+          <t>Món Quà Chia Tay I</t>
         </is>
       </c>
       <c r="N465" t="inlineStr">
@@ -33054,7 +33054,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Parting Gift II</t>
+          <t>Món Quà Chia Tay II</t>
         </is>
       </c>
       <c r="N466" t="inlineStr">
@@ -33124,7 +33124,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Lethal Core I</t>
+          <t>Lõi Sát Thủ I</t>
         </is>
       </c>
       <c r="N467" t="inlineStr">
@@ -33194,7 +33194,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Lethal Core II</t>
+          <t>Lõi Sát Thủ II</t>
         </is>
       </c>
       <c r="N468" t="inlineStr">
@@ -33264,7 +33264,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Sức Mạnh Của Sấm Sét</t>
+          <t>Sấm Sét Uy Lực</t>
         </is>
       </c>
       <c r="N469" t="inlineStr">
@@ -33334,7 +33334,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Tempest Mephis: Ultra</t>
+          <t>Mephis Bão Tố: Siêu Cấp</t>
         </is>
       </c>
       <c r="N470" t="inlineStr">
@@ -33404,7 +33404,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Repulse II</t>
+          <t>Đẩy Lùi II</t>
         </is>
       </c>
       <c r="N471" t="inlineStr">
@@ -33474,7 +33474,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Special Tactics I</t>
+          <t>Chiến Thuật Đặc Biệt I</t>
         </is>
       </c>
       <c r="N472" t="inlineStr">
@@ -33544,7 +33544,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Special Tactics II</t>
+          <t>Chiến Thuật Đặc Biệt II</t>
         </is>
       </c>
       <c r="N473" t="inlineStr">
@@ -33614,7 +33614,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Special Tactics III</t>
+          <t>Chiến Thuật Đặc Biệt III</t>
         </is>
       </c>
       <c r="N474" t="inlineStr">
@@ -33684,7 +33684,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Shattered Dreams I</t>
+          <t>Giấc Mộng Tan Vỡ I</t>
         </is>
       </c>
       <c r="N475" t="inlineStr">
@@ -33754,7 +33754,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Shattered Dreams II</t>
+          <t>Giấc Mộng Tan Vỡ II</t>
         </is>
       </c>
       <c r="N476" t="inlineStr">
@@ -33824,7 +33824,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Shattered Dreams III</t>
+          <t>Giấc Mộng Tan Vỡ III</t>
         </is>
       </c>
       <c r="N477" t="inlineStr">
@@ -33894,7 +33894,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Extended Protection</t>
+          <t>Bảo Vệ Mở Rộng</t>
         </is>
       </c>
       <c r="N478" t="inlineStr">
@@ -33964,7 +33964,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Shielding I</t>
+          <t>Bảo Vệ I</t>
         </is>
       </c>
       <c r="N479" t="inlineStr">
@@ -34034,7 +34034,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Shielding II</t>
+          <t>Bảo Vệ II</t>
         </is>
       </c>
       <c r="N480" t="inlineStr">
@@ -34244,7 +34244,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Hơi Thở Của Sự Mục Nát</t>
+          <t>Hơi Thở Của Sự Suy Tàn</t>
         </is>
       </c>
       <c r="N483" t="inlineStr">
@@ -34314,7 +34314,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Dragon of Dirge: Ultra</t>
+          <t>Rồng của Bi Ca: Siêu Cấp</t>
         </is>
       </c>
       <c r="N484" t="inlineStr">
@@ -34384,7 +34384,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Singularity I</t>
+          <t>Kỳ Dị Cấp I</t>
         </is>
       </c>
       <c r="N485" t="inlineStr">
@@ -34454,7 +34454,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Singularity II</t>
+          <t>Kỳ Dị Cấp II</t>
         </is>
       </c>
       <c r="N486" t="inlineStr">
@@ -34524,7 +34524,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Fallout I</t>
+          <t>Hậu quả I</t>
         </is>
       </c>
       <c r="N487" t="inlineStr">
@@ -34594,7 +34594,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Fallout II</t>
+          <t>Hậu quả II</t>
         </is>
       </c>
       <c r="N488" t="inlineStr">
@@ -34664,7 +34664,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Fallout III</t>
+          <t>Hậu quả III</t>
         </is>
       </c>
       <c r="N489" t="inlineStr">
@@ -34734,7 +34734,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Joint Tactics I</t>
+          <t>Chiến Thuật Đồng Bộ I</t>
         </is>
       </c>
       <c r="N490" t="inlineStr">
@@ -34804,7 +34804,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Joint Tactics II</t>
+          <t>Chiến Thuật Đồng Bộ II</t>
         </is>
       </c>
       <c r="N491" t="inlineStr">
@@ -34874,7 +34874,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Joint Tactics III</t>
+          <t>Chiến Thuật Đồng Bộ III</t>
         </is>
       </c>
       <c r="N492" t="inlineStr">
@@ -34944,7 +34944,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Reinforcing Strike</t>
+          <t>Đòn Tấn Công Tăng Cường</t>
         </is>
       </c>
       <c r="N493" t="inlineStr">
@@ -35014,7 +35014,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Thunder of Bane I</t>
+          <t>Sấm Sét Tận Thế I</t>
         </is>
       </c>
       <c r="N494" t="inlineStr">
@@ -35084,7 +35084,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Thunder of Bane II</t>
+          <t>Sấm Sét Tận Thế II</t>
         </is>
       </c>
       <c r="N495" t="inlineStr">
@@ -35154,7 +35154,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Vampirism I</t>
+          <t>Huyết Năng I</t>
         </is>
       </c>
       <c r="N496" t="inlineStr">
@@ -35224,7 +35224,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Vampirism II</t>
+          <t>Huyết Năng II</t>
         </is>
       </c>
       <c r="N497" t="inlineStr">
@@ -35294,7 +35294,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Cảm Giác Lạnh Buốt</t>
+          <t>Hơi Lạnh Đắng Cay</t>
         </is>
       </c>
       <c r="N498" t="inlineStr">
@@ -35364,7 +35364,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Sentry Construct: Ultra</t>
+          <t>Công Trình Tuần Tra: Ultra</t>
         </is>
       </c>
       <c r="N499" t="inlineStr">
@@ -35434,7 +35434,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Ironclad I</t>
+          <t>Thép Bọc I</t>
         </is>
       </c>
       <c r="N500" t="inlineStr">
@@ -35504,7 +35504,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Ironclad II</t>
+          <t>Thép Bọc II</t>
         </is>
       </c>
       <c r="N501" t="inlineStr">
